--- a/docs/CodeSystem-ahip-demo-additional-religion-codes.xlsx
+++ b/docs/CodeSystem-ahip-demo-additional-religion-codes.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
